--- a/exports/colleges/25881_iit-madras-indian-institute-of-technology-iitm-chennai.xlsx
+++ b/exports/colleges/25881_iit-madras-indian-institute-of-technology-iitm-chennai.xlsx
@@ -445,7 +445,7 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="159" customWidth="1" min="13" max="13"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #15</t>
+          <t>Rank #1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="93" customWidth="1" min="3" max="3"/>
+    <col width="93" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="108" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>2.67 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Graduation + GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GATE, COAP</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 25 Apr 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>10.71 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 75% + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bachelor of Science [BS]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.4 Lakhs</t>
+          <t>9.4 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10+2 + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Jan - 25 Sept 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Science</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>2.77 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Post Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>11 Nov - 28 Mar 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.49 Lakhs</t>
+          <t>11.49 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10+2 + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Jan - 25 Sept 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.97 Lakhs - 2.67 Lakhs</t>
+          <t>2.67 L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.71 Lakhs - 16.91 Lakhs</t>
+          <t>11.88 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Master of Arts [MA]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Master of Arts [MA]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.97 Lakhs - 2.77 Lakhs</t>
+          <t>2.47 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 25 Apr 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BS + MS</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BS + MS</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.4 Lakhs - 11.49 Lakhs</t>
+          <t>12.91 L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NEET PG</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Aug - 13 Sept 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.97 Lakhs - 2.67 Lakhs</t>
+          <t>10.71 L</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Jan - 25 Sept 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.47 Lakhs</t>
+          <t>16.91 L</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1379,27 +1379,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12.91 Lakhs</t>
+          <t>19.05 L</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>6 Sept - 26 Oct 2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1436,32 +1436,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17 Lakhs - 19.05 Lakhs</t>
+          <t>1.97 L</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>11 Nov - 28 Mar 2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1498,27 +1498,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Diploma</t>
+          <t>Management Development Programme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diploma</t>
+          <t>Management Development Programme</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Diploma</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1560,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.9 Lakhs</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>8 months</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1622,32 +1622,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrial Mathematics &amp; Scientific Computing</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Industrial Mathematics &amp; Scientific Computing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>2.77 L</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>11 Nov - 28 Mar 2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1684,32 +1684,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Post Graduate Diploma in Artificial Intelligence &amp; Machine Learning</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Data Science</t>
+          <t>Post Graduate Diploma in Artificial Intelligence &amp; Machine Learning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Data Science</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>5.9 L</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + GATE</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE, COAP</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Microelectronics And Vlsi Design</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Microelectronics And Vlsi Design</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 75% + JEE Advanced</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1870,42 +1870,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>9.4 Lakhs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 + JEE Advanced</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1932,27 +1932,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Aerospace Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aerospace Engineering</t>
+          <t>M.Phil/Ph.D in Science</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1994,27 +1994,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mechanical Design</t>
+          <t>Bachelor of Science [BS] + Master of Science [MS]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mechanical Design</t>
+          <t>Bachelor of Science [BS] + Master of Science [MS]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>11.49 Lakhs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 + JEE Advanced</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2061,17 +2061,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Electronic System Design and Instrumentation</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Electronic System Design and Instrumentation</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>1.97 Lakhs - 2.67 Lakhs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2118,27 +2118,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>10.71 Lakhs - 16.91 Lakhs</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2180,27 +2180,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Building Technology And Construction Management</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Building Technology And Construction Management</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>1.97 Lakhs - 2.77 Lakhs</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2242,27 +2242,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Power Systems And Power Electronics</t>
+          <t>BS + MS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Power Systems And Power Electronics</t>
+          <t>BS + MS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>9.4 Lakhs - 11.49 Lakhs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2304,22 +2304,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Petroleum Engineering</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Petroleum Engineering</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>1.97 Lakhs - 2.67 Lakhs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Communication And Signal Processing</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Communication And Signal Processing</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>2.47 Lakhs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2428,22 +2428,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Computational and Experimental Mechanics</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Computational and Experimental Mechanics</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>12.91 Lakhs</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>17 Lakhs - 19.05 Lakhs</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2552,27 +2552,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2.67 Lakhs</t>
+          <t>5.9 Lakhs</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nanotechnology</t>
+          <t>Industrial Mathematics &amp; Scientific Computing</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Nanotechnology</t>
+          <t>Industrial Mathematics &amp; Scientific Computing</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RF and Photonics</t>
+          <t>Artificial Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RF and Photonics</t>
+          <t>Artificial Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Metallurgical &amp; Materials Engineering</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Metallurgical &amp; Materials Engineering</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bioprocess</t>
+          <t>Microelectronics And Vlsi Design</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bioprocess</t>
+          <t>Microelectronics And Vlsi Design</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Aerospace Engineering</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Aerospace Engineering</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Control &amp; Optimization</t>
+          <t>Mechanical Design</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Control &amp; Optimization</t>
+          <t>Mechanical Design</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering</t>
+          <t>Electronic System Design and Instrumentation</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering</t>
+          <t>Electronic System Design and Instrumentation</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ocean Structures</t>
+          <t>Building Technology And Construction Management</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ocean Structures</t>
+          <t>Building Technology And Construction Management</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ocean Technology And Management</t>
+          <t>Power Systems And Power Electronics</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ocean Technology And Management</t>
+          <t>Power Systems And Power Electronics</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Advanced Materials Science &amp; Technology</t>
+          <t>Petroleum Engineering</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Advanced Materials Science &amp; Technology</t>
+          <t>Petroleum Engineering</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Aerodynamics</t>
+          <t>Communication And Signal Processing</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aerodynamics</t>
+          <t>Communication And Signal Processing</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Automotive Engineering</t>
+          <t>Computational and Experimental Mechanics</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Automotive Engineering</t>
+          <t>Computational and Experimental Mechanics</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Computational Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Computational Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dynamics &amp; Control</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Dynamics &amp; Control</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Electrical Vehicle Engineering</t>
+          <t>Nanotechnology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Electrical Vehicle Engineering</t>
+          <t>Nanotechnology</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Energy System Engineering</t>
+          <t>RF and Photonics</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Energy System Engineering</t>
+          <t>RF and Photonics</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hydraulics &amp; Water Resource Engineering</t>
+          <t>Metallurgical &amp; Materials Engineering</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Hydraulics &amp; Water Resource Engineering</t>
+          <t>Metallurgical &amp; Materials Engineering</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Industrial Metallurgy</t>
+          <t>Bioprocess</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Industrial Metallurgy</t>
+          <t>Bioprocess</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Quantum Technology</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Quantum Technology</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Robotics Engineering</t>
+          <t>Control &amp; Optimization</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Robotics Engineering</t>
+          <t>Control &amp; Optimization</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Semiconductor Technology</t>
+          <t>Geotechnical Engineering</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Semiconductor Technology</t>
+          <t>Geotechnical Engineering</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vlsi Technology</t>
+          <t>Manufacturing Engineering</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Vlsi Technology</t>
+          <t>Manufacturing Engineering</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4288,27 +4288,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Ocean Structures</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Ocean Structures</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4350,27 +4350,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Aerospace Engineering</t>
+          <t>Ocean Technology And Management</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Aerospace Engineering</t>
+          <t>Ocean Technology And Management</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4412,27 +4412,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Advanced Materials Science &amp; Technology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Advanced Materials Science &amp; Technology</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4474,27 +4474,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Aerodynamics</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Aerodynamics</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4536,27 +4536,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Naval Architecture &amp; Ocean Engineering</t>
+          <t>Automotive Engineering</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Naval Architecture &amp; Ocean Engineering</t>
+          <t>Automotive Engineering</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4598,27 +4598,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4660,27 +4660,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Computational Engineering</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Computational Engineering</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4722,27 +4722,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Biological Engineering</t>
+          <t>Dynamics &amp; Control</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Biological Engineering</t>
+          <t>Dynamics &amp; Control</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4784,27 +4784,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Vehicle Engineering</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Vehicle Engineering</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4846,27 +4846,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Metallurgical And Materials Engineering</t>
+          <t>Energy System Engineering</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Metallurgical And Materials Engineering</t>
+          <t>Energy System Engineering</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4908,27 +4908,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Computational Engineering</t>
+          <t>Hydraulics &amp; Water Resource Engineering</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Computational Engineering</t>
+          <t>Hydraulics &amp; Water Resource Engineering</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4970,27 +4970,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Biomedical Instrumentation</t>
+          <t>Industrial Metallurgy</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Biomedical Instrumentation</t>
+          <t>Industrial Metallurgy</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5032,27 +5032,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ph.D Biotechnology</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ph.D Biotechnology</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5094,27 +5094,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ph.D Physics</t>
+          <t>Quantum Technology</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ph.D Physics</t>
+          <t>Quantum Technology</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5156,27 +5156,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ph.D Chemistry</t>
+          <t>Robotics Engineering</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ph.D Chemistry</t>
+          <t>Robotics Engineering</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5218,27 +5218,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ph.D Mathematics</t>
+          <t>Semiconductor Technology</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ph.D Mathematics</t>
+          <t>Semiconductor Technology</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5280,27 +5280,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ph.D Civil Engineering</t>
+          <t>Vlsi Technology</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ph.D Civil Engineering</t>
+          <t>Vlsi Technology</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>2.67 Lakhs</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5342,27 +5342,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5404,27 +5404,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Aerospace Engineering</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Aerospace Engineering</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5466,27 +5466,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Management Studies</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Management Studies</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5528,27 +5528,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5590,27 +5590,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Naval Architecture &amp; Ocean Engineering</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Naval Architecture &amp; Ocean Engineering</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5652,27 +5652,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5714,27 +5714,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Engineering Design</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Engineering Design</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Engineering Design</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5776,27 +5776,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Metallurgical Engineering And Materials Science</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Metallurgical Engineering And Materials Science</t>
+          <t>Biological Engineering</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Metallurgical Engineering And Materials Science</t>
+          <t>Biological Engineering</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5838,27 +5838,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5900,27 +5900,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Climate &amp; Ocean Science</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Climate &amp; Ocean Science</t>
+          <t>Metallurgical And Materials Engineering</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Climate &amp; Ocean Science</t>
+          <t>Metallurgical And Materials Engineering</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5962,27 +5962,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Data Science</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Data Science</t>
+          <t>Computational Engineering</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Data Science</t>
+          <t>Computational Engineering</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6024,27 +6024,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Interdisciplinary</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Interdisciplinary</t>
+          <t>Biomedical Instrumentation</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Interdisciplinary</t>
+          <t>Biomedical Instrumentation</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2.77 Lakhs</t>
+          <t>10.71 Lakhs</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Medical Sciences</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Medical Sciences</t>
+          <t>Ph.D Biotechnology</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Medical Sciences</t>
+          <t>Ph.D Biotechnology</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6148,25 +6148,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BS + MS</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BS + MS (General)</t>
+          <t>Ph.D Physics</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Ph.D Physics</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9.4 Lakhs - 11.49 Lakhs</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>2.77 Lakhs</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -6179,7 +6183,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6194,7 +6198,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6206,25 +6210,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>M.Sc (General)</t>
+          <t>Ph.D Chemistry</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Ph.D Chemistry</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.97 Lakhs - 2.67 Lakhs</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>2.77 Lakhs</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -6237,7 +6245,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6252,7 +6260,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6264,25 +6272,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MA (General)</t>
+          <t>Ph.D Mathematics</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Ph.D Mathematics</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2.47 Lakhs</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
+          <t>2.77 Lakhs</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -6295,7 +6307,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6310,7 +6322,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6322,27 +6334,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MBA (General)</t>
+          <t>Ph.D Civil Engineering</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Ph.D Civil Engineering</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>12.91 Lakhs</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6357,7 +6369,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6372,7 +6384,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6384,27 +6396,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12.91 Lakhs</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6414,12 +6426,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6434,7 +6446,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6446,27 +6458,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>12.91 Lakhs</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6476,12 +6488,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6496,7 +6508,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6508,32 +6520,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>Management Studies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EMBA (General)</t>
+          <t>Management Studies</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Management Studies</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>17 Lakhs - 19.05 Lakhs</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6543,7 +6555,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6558,7 +6570,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6570,25 +6582,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Diploma</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Diploma (General)</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>93,000</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+          <t>2.77 Lakhs</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -6628,25 +6644,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PG Diploma (General)</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>5.9 Lakhs</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>2.77 Lakhs</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -6686,27 +6706,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B.E./B.Tech</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>B.E./B.Tech</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Core engineering, many specializations</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6721,7 +6741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6748,27 +6768,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Engineering Design</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MBA/PGDM</t>
+          <t>Engineering Design</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>MBA/PGDM</t>
+          <t>Engineering Design</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Management, leadership, analytics</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6783,7 +6803,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6798,7 +6818,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6810,27 +6830,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>Metallurgical Engineering And Materials Science</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B.Sc. (AI/Data Science)</t>
+          <t>Metallurgical Engineering And Materials Science</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B.Sc. (AI/Data Science)</t>
+          <t>Metallurgical Engineering And Materials Science</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Science, tech, data focus</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6872,27 +6892,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>IT, software, data science</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6922,7 +6942,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6934,27 +6954,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>Climate &amp; Ocean Science</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Online B.Sc in Programming and Data Science</t>
+          <t>Climate &amp; Ocean Science</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Online B.Sc in Programming and Data Science</t>
+          <t>Climate &amp; Ocean Science</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6964,7 +6984,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(10+2) qualification with minimum passing percentage, with Mathematics and English as mandatory subjects.</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6996,27 +7016,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Online Diploma in Programming</t>
+          <t>Artificial Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Online Diploma in Programming</t>
+          <t>Artificial Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Online Diploma in Programming</t>
+          <t>Artificial Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>8 months</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7026,7 +7046,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>At least two years of any UG education.</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7046,7 +7066,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -7058,27 +7078,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Online Diploma in Data Science</t>
+          <t>Interdisciplinary</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Online Diploma in Data Science</t>
+          <t>Interdisciplinary</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Online Diploma in Data Science</t>
+          <t>Interdisciplinary</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>8 months</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7088,7 +7108,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>At least two years of any UG education.</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7108,7 +7128,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -7120,22 +7140,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BTech</t>
+          <t>Medical Sciences</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BTech</t>
+          <t>Medical Sciences</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>BTech</t>
+          <t>Medical Sciences</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.04 Lakhs (1st Year Fees)</t>
+          <t>2.77 Lakhs</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7182,55 +7202,1089 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>BS + MS</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BS + MS (General)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>9.4 Lakhs - 11.49 Lakhs</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>M.Sc (General)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.97 Lakhs - 2.67 Lakhs</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MA (General)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2.47 Lakhs</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MBA (General)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>12.91 Lakhs</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>12.91 Lakhs</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>12.91 Lakhs</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EMBA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>EMBA (General)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>17 Lakhs - 19.05 Lakhs</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Diploma (General)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>93,000</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PG Diploma</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PG Diploma (General)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>5.9 Lakhs</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>B.E./B.Tech</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>B.E./B.Tech</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Core engineering, many specializations</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>JEE Advanced</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>MBA/PGDM</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>MBA/PGDM</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Management, leadership, analytics</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>B.Sc. (AI/Data Science)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>B.Sc. (AI/Data Science)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Science, tech, data focus</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>IT, software, data science</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Online B.Sc in Programming and Data Science</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Online B.Sc in Programming and Data Science</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(10+2) qualification with minimum passing percentage, with Mathematics and English as mandatory subjects.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Online Diploma in Programming</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Online Diploma in Programming</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Online Diploma in Programming</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>8 months</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>At least two years of any UG education.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Online Diploma in Data Science</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Online Diploma in Data Science</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Online Diploma in Data Science</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>8 months</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>At least two years of any UG education.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BTech</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BTech</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BTech</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1.04 Lakhs (1st Year Fees)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>25881</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>MTech</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>MTech</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>MTech</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>24,600 (1st Year Fees)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
@@ -7384,12 +8438,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4,30,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21,48,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -7419,13 +8473,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7436,17 +8488,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ranking_body</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ranking_year</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -7458,15 +8500,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Collegedunia</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CD Rank #15</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>No Data Available</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
